--- a/public_administration_forms/011_government_workforce_diversity_employment_analysis--public_administration_forms.xlsx
+++ b/public_administration_forms/011_government_workforce_diversity_employment_analysis--public_administration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1162,8 +1162,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'a',_'text':_'a'}</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'A', 'text': 'A'}</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'b',_'text':_'b'}</t>
+          <t>b</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'B', 'text': 'B'}</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'c',_'text':_'c'}</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'C', 'text': 'C'}</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1276,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'1',_'text':_'1'}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': '1', 'text': '1'}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'2',_'text':_'2'}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': '2', 'text': '2'}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'3',_'text':_'3'}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': '3', 'text': '3'}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'m',_'text':_'male'}</t>
+          <t>m</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'M', 'text': 'Male'}</t>
+          <t>M</t>
         </is>
       </c>
     </row>
@@ -1378,12 +1378,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'f',_'text':_'female'}</t>
+          <t>f</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'F', 'text': 'Female'}</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -1395,12 +1395,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'o',_'text':_'other'}</t>
+          <t>o</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'O', 'text': 'Other'}</t>
+          <t>O</t>
         </is>
       </c>
     </row>
